--- a/content/tz-kak-obrashchatsya-k-kitaycam-po-imeni.xlsx
+++ b/content/tz-kak-obrashchatsya-k-kitaycam-po-imeni.xlsx
@@ -650,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -877,7 +877,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ЧАСТИЧНО ЗАНЯТО — см. поправку ниже</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -901,30 +901,79 @@
       <c r="C21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>УГОЛ СТАТЬИ</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>САМО ИМЯ. Ни «Этикет», ни «Деловое письмо» не объясняют, из чего китайское имя состоит и почему порядок именно такой. Они учат, что сказать, но не объясняют, с чем вы имеете дело</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
       <c r="C22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>ПОПРАВКА, внесена после написания статьи</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Первая версия листа утверждала, что 小姐 в блоге не разобрано. ЭТО НЕВЕРНО: в «Деловом письме китайскому партнёру» слово встречается трижды, в том числе вопросом в FAQ «Можно ли обращаться 小姐 к женщине?» с ответом «в материковом Китае лучше не стоит, безопасный вариант 女士»</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ЧТО ЭТО МЕНЯЕТ</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Угол сохраняется: «Деловое письмо» закрывает 小姐 для ПИСЬМЕННОЙ речи одной строкой запрета. Новая статья даёт устную сторону: 王小姐 с фамилией нареканий обычно не вызывает, замена в кафе и магазине (服务员), 美女 не для переговорной, в Гонконге и на Тайване употребление другое</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ЧТО ДОБАВЛЕНО В ТЕКСТ</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>В раздел про 小姐 вписана строка «А в деловой переписке этого послабления нет: там безопасный вариант один — 女士» со ссылкой на разбор письма. Без неё читатель двух наших страниц увидел бы противоречие</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>УГОЛ СТАТЬИ</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>САМО ИМЯ. Ни «Этикет», ни «Деловое письмо» не объясняют, из чего китайское имя состоит и почему порядок именно такой. Они учат, что сказать, но не объясняют, с чем вы имеете дело</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>РЕШЕНИЕ</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Отдельная статья про устройство имени и выбор формы обращения. «Этикет вообще» и «формулы письма» отдаём ссылками. Повторять 老/小 и 您 не будем — они уже разобраны</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1023,7 +1072,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>предупреждение про 小姐, которого в блоге нет ни в одной статье</t>
+          <t>предупреждение про 小姐. Оговорка: одной строкой оно есть и в «Деловом письме», но только для письменной речи — см. поправку на листе 2</t>
         </is>
       </c>
     </row>
